--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B2" t="n">
-        <v>103308</v>
+        <v>103311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R2" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299949</v>
+        <v>123299953</v>
       </c>
       <c r="B3" t="n">
-        <v>103308</v>
+        <v>103311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620043</v>
+        <v>620067</v>
       </c>
       <c r="R3" t="n">
-        <v>6713721</v>
+        <v>6713666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -948,7 +948,7 @@
         <v>123299946</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299949</v>
+        <v>123299946</v>
       </c>
       <c r="B2" t="n">
-        <v>103311</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620043</v>
+        <v>620042</v>
       </c>
       <c r="R2" t="n">
-        <v>6713721</v>
+        <v>6713717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -813,7 +804,7 @@
         <v>123299953</v>
       </c>
       <c r="B3" t="n">
-        <v>103311</v>
+        <v>103313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -945,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299946</v>
+        <v>123299949</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>103313</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,38 +948,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620042</v>
+        <v>620043</v>
       </c>
       <c r="R4" t="n">
-        <v>6713717</v>
+        <v>6713721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>123299953</v>
       </c>
       <c r="B3" t="n">
-        <v>103313</v>
+        <v>103319</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>123299949</v>
       </c>
       <c r="B4" t="n">
-        <v>103313</v>
+        <v>103319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299946</v>
+        <v>123299949</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>103322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620042</v>
+        <v>620043</v>
       </c>
       <c r="R2" t="n">
-        <v>6713717</v>
+        <v>6713721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299953</v>
+        <v>123299946</v>
       </c>
       <c r="B3" t="n">
-        <v>103319</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +822,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620067</v>
+        <v>620042</v>
       </c>
       <c r="R3" t="n">
-        <v>6713666</v>
+        <v>6713717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299949</v>
+        <v>123299953</v>
       </c>
       <c r="B4" t="n">
-        <v>103319</v>
+        <v>103322</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620043</v>
+        <v>620067</v>
       </c>
       <c r="R4" t="n">
-        <v>6713721</v>
+        <v>6713666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299949</v>
+        <v>123299946</v>
       </c>
       <c r="B2" t="n">
-        <v>103322</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620043</v>
+        <v>620042</v>
       </c>
       <c r="R2" t="n">
-        <v>6713721</v>
+        <v>6713717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299946</v>
+        <v>123299953</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>103339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620042</v>
+        <v>620067</v>
       </c>
       <c r="R3" t="n">
-        <v>6713717</v>
+        <v>6713666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B4" t="n">
-        <v>103322</v>
+        <v>103339</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R4" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299946</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B3" t="n">
-        <v>103339</v>
+        <v>103021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R3" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299949</v>
+        <v>123299953</v>
       </c>
       <c r="B4" t="n">
-        <v>103339</v>
+        <v>103021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620043</v>
+        <v>620067</v>
       </c>
       <c r="R4" t="n">
-        <v>6713721</v>
+        <v>6713666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299946</v>
+        <v>123299953</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>103023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620042</v>
+        <v>620067</v>
       </c>
       <c r="R2" t="n">
-        <v>6713717</v>
+        <v>6713666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299949</v>
+        <v>123299946</v>
       </c>
       <c r="B3" t="n">
-        <v>103021</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +822,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620043</v>
+        <v>620042</v>
       </c>
       <c r="R3" t="n">
-        <v>6713721</v>
+        <v>6713717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B4" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R4" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299953</v>
+        <v>123299946</v>
       </c>
       <c r="B2" t="n">
-        <v>103023</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620067</v>
+        <v>620042</v>
       </c>
       <c r="R2" t="n">
-        <v>6713666</v>
+        <v>6713717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299946</v>
+        <v>123299953</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>102598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620042</v>
+        <v>620067</v>
       </c>
       <c r="R3" t="n">
-        <v>6713717</v>
+        <v>6713666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -939,7 +939,7 @@
         <v>123299949</v>
       </c>
       <c r="B4" t="n">
-        <v>103023</v>
+        <v>102598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B3" t="n">
         <v>102598</v>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R3" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299949</v>
+        <v>123299953</v>
       </c>
       <c r="B4" t="n">
         <v>102598</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620043</v>
+        <v>620067</v>
       </c>
       <c r="R4" t="n">
-        <v>6713721</v>
+        <v>6713666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299946</v>
+        <v>123299953</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>102598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620042</v>
+        <v>620067</v>
       </c>
       <c r="R2" t="n">
-        <v>6713717</v>
+        <v>6713666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299949</v>
+        <v>123299946</v>
       </c>
       <c r="B3" t="n">
-        <v>102598</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +822,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620043</v>
+        <v>620042</v>
       </c>
       <c r="R3" t="n">
-        <v>6713721</v>
+        <v>6713717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B4" t="n">
         <v>102598</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R4" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299953</v>
+        <v>123299949</v>
       </c>
       <c r="B2" t="n">
-        <v>102598</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620067</v>
+        <v>620043</v>
       </c>
       <c r="R2" t="n">
-        <v>6713666</v>
+        <v>6713721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,50 +805,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299946</v>
+        <v>123299953</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1666</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sumpviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Viola uliginosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620042</v>
+        <v>620067</v>
       </c>
       <c r="R3" t="n">
-        <v>6713717</v>
+        <v>6713666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -890,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>på hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Nike Nylander</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -936,59 +935,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299949</v>
+        <v>123299946</v>
       </c>
       <c r="B4" t="n">
-        <v>102598</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1666</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sumpviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola uliginosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>V. Römossen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620043</v>
+        <v>620042</v>
       </c>
       <c r="R4" t="n">
-        <v>6713721</v>
+        <v>6713717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,7 +1000,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1025,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,12 +1020,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på hygge</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,7 +1045,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Elsa Fogelström</t>
+          <t>Linnéa Kjellberg, Nike Nylander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 40023-2021 artfynd.xlsx
+++ b/artfynd/A 40023-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123299949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123299953</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,8 +1068,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123299946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>